--- a/tools/importer/reports/import-library-docs.report.xlsx
+++ b/tools/importer/reports/import-library-docs.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="135">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,7 +58,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-29T03:05:30.105Z</t>
+    <t>2026-10-29T15:33:53.284Z</t>
   </si>
   <si>
     <t>https://www.sfu.ca/</t>
@@ -118,7 +118,7 @@
     <t>programs-sidenav</t>
   </si>
   <si>
-    <t>2026-10-29T00:31:18.120Z</t>
+    <t>2026-10-29T15:33:43.066Z</t>
   </si>
   <si>
     <t>fragments/promo-canada.report.json</t>
@@ -259,7 +259,7 @@
     <t>docs/library/blocks/cards</t>
   </si>
   <si>
-    <t>2026-10-29T03:05:48.263Z</t>
+    <t>2026-10-29T15:34:11.022Z</t>
   </si>
   <si>
     <t>https://www.sfu.ca/?libdoc=cards</t>
@@ -361,7 +361,7 @@
     <t>docs/library/blocks/sidenav</t>
   </si>
   <si>
-    <t>2026-10-29T03:06:16.382Z</t>
+    <t>2026-10-29T15:34:02.889Z</t>
   </si>
   <si>
     <t>https://www.sfu.ca/?libdoc=sidenav</t>
@@ -380,6 +380,42 @@
   </si>
   <si>
     <t>https://www.sfu.ca/?libdoc=stats</t>
+  </si>
+  <si>
+    <t>docs/library/templates/landing-page.report.json</t>
+  </si>
+  <si>
+    <t>docs/library/templates/landing-page</t>
+  </si>
+  <si>
+    <t>2026-10-29T03:06:50.552Z</t>
+  </si>
+  <si>
+    <t>https://www.sfu.ca/?target=library</t>
+  </si>
+  <si>
+    <t>docs/library/templates/programs.report.json</t>
+  </si>
+  <si>
+    <t>docs/library/templates/programs</t>
+  </si>
+  <si>
+    <t>2026-10-29T03:07:00.204Z</t>
+  </si>
+  <si>
+    <t>https://www.sfu.ca/beedie/programs/undergraduate/bba-major/program.html?target=library</t>
+  </si>
+  <si>
+    <t>docs/library/templates/resources.report.json</t>
+  </si>
+  <si>
+    <t>docs/library/templates/resources</t>
+  </si>
+  <si>
+    <t>2026-10-29T03:07:09.328Z</t>
+  </si>
+  <si>
+    <t>https://www.sfu.ca/research/researcher-resources/resources/research-facilities.html?target=library</t>
   </si>
 </sst>
 </file>
@@ -768,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1657,6 +1693,111 @@
         <v>122</v>
       </c>
     </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" t="s">
+        <v>125</v>
+      </c>
+      <c r="J26" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-library-docs.report.xlsx
+++ b/tools/importer/reports/import-library-docs.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="140">
   <si>
     <t>_reportFile</t>
   </si>
@@ -380,6 +380,21 @@
   </si>
   <si>
     <t>https://www.sfu.ca/?libdoc=stats</t>
+  </si>
+  <si>
+    <t>docs/library/blocks/teaser.report.json</t>
+  </si>
+  <si>
+    <t>teaser</t>
+  </si>
+  <si>
+    <t>docs/library/blocks/teaser</t>
+  </si>
+  <si>
+    <t>2026-10-29T17:07:54.223Z</t>
+  </si>
+  <si>
+    <t>https://www.sfu.ca/?libdoc=teaser</t>
   </si>
   <si>
     <t>docs/library/templates/landing-page.report.json</t>
@@ -804,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1698,13 +1713,13 @@
         <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -1716,21 +1731,21 @@
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J26" t="s">
         <v>12</v>
       </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -1739,7 +1754,7 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -1751,21 +1766,21 @@
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J27" t="s">
         <v>12</v>
       </c>
       <c r="K27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -1774,7 +1789,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -1786,16 +1801,51 @@
         <v>14</v>
       </c>
       <c r="H28" t="s">
+        <v>67</v>
+      </c>
+      <c r="I28" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s">
         <v>71</v>
       </c>
-      <c r="I28" t="s">
-        <v>133</v>
-      </c>
-      <c r="J28" t="s">
-        <v>12</v>
-      </c>
-      <c r="K28" t="s">
-        <v>134</v>
+      <c r="I29" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
